--- a/docs/golden-set/2026-10-14-baroque-blind.xlsx
+++ b/docs/golden-set/2026-10-14-baroque-blind.xlsx
@@ -11246,7 +11246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -11283,14 +11283,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>盲標序已打亂，與系統排名無關；請勿參考任何系統輸出或 LLM。</t>
+          <t>盲標序已打亂，與系統排名無關；請勿使用本系統、參考任何系統輸出或請 LLM 代為判斷。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>標完約 2 週後會再抽 10%（37–40 筆）重標，計算一致性（目標 κ ≥ 0.7）。</t>
+          <t>由 2 位標註者各自獨立標註（標完前不互相討論、不交換檔案），用來計算兩人一致性 Cohen's κ（目標 ≥ 0.7）；意見不同的項目最後由第三人或兩人討論裁定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>可以查（鼓勵）：為了看懂題目而查背景知識（例：卡拉契家族有誰、濕壁畫是什麼）；用翻譯工具讀懂英文館藏說明；查文件中的作品是不是題目問的那一件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>不可以：直接照搬搜尋結果或 AI 的回答當作分數。分數依「這一筆文件本身能不能回答這一題」由你判斷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>可分次標註（一次標完一題為單位）；標完存檔交回即可。檔名請加上你的名字縮寫。</t>
         </is>
       </c>
     </row>
